--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45204</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>45492</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45705</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45609</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45490</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>46041</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45646</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45705</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45832</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45882</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>44867</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45672</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>46153</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45219</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45832</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45939</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>46149</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>44469</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>46148</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>46167</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>46239</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>45890</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46008</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>44714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>46150</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>46008</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45351</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46157</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>46204</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>45785</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46150</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45219</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>46030</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>45709</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>45040</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45592</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>46008</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>45531</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>46251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>45783</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45947</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>44858</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>45901</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>46022</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>46000</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45877</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45376</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>46089</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45833</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45904</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>45937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>45966</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44509</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>46154</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>45987</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>46128</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>46211</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45782</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45376</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>44827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44498</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>46089</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44620</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44847</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45299</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45903</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45492</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46085</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>46148</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45960</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45966</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45966</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>46027</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45160</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>46199</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44981</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>46211</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>46211</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>45628</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>46224</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45842</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44784</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44622</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44742</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>44460</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>44629</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>44473</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44496</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44727</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44469</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44466</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44564</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44477</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>44715</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44617</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44466</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44872</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>44655</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>44838</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44461</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44461</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44526</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44735</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44497</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44497</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44545</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44729</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44888</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>45484</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45595</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>45229</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44481</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45314</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45212</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45306</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45757</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45736</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>45209</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>44903</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45353</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44987</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>44952</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>44896</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45758</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45222</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45264</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45274</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45407</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45132</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45099</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>45223</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>45477</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45610</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>45441</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45601</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>44987</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45744</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44854</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45149</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45678</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45226</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44844</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45267</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45223</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45301</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44788</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44985</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>44460</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45233</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44644</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45135</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>45481</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45316</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>44951</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45159</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45422</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45222</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>44545</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>46066</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44914</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45660</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45705</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44693</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>45647</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45782</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>45775</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45138</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45705</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45887</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45152</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45593</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45698</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>46139</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44644</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45887</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44644</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45353</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45645</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45840</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45894</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>46139</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45894</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45896</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45744</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45903</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45902</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45862</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45697</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45768</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45904</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>46092</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>46049</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46044</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45736</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45797</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45793</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45848</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45903</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45915</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>46041</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45915</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45278</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45915</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44484</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45209</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45923</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>44831</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45758</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45979</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45103</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45881</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45628</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45411</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>44467</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45932</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>44964</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>46146</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46146</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>46147</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>46148</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45316</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45628</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45947</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45950</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>46150</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45954</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45956</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45217</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45986</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45960</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45964</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>44875</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45699</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>46155</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45223</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45966</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45966</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45968</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45544</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45971</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45971</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45544</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45040</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45610</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45975</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45974</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44460</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45975</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45974</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45975</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45980</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>46154</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>46155</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>46155</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45695</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45113</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45986</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45987</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45180</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45986</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45987</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45986</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>44627</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>46157</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45537</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45986</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45987</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45986</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45988</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45988</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45988</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>46161</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>46160</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45610</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>46163</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>46163</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45994</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>45303</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>45593</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45999</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45834</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45374</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45999</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45586</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>45239</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45072</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45146</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45203</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45593</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45453</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45206</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45674</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45113</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45113</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45113</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45999</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45104</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45593</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45252</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45950</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45453</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45159</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>46167</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45113</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>46167</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>46164</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45111</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45014</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45688</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>46164</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>46164</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>46009</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>46008</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45678</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>46008</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>46008</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>46008</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>46009</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46010</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46013</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>44917</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>46024</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>46024</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>44641</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44813</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46174</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46171</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46174</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>46174</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46036</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>46016</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45638</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45638</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>46042</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>46044</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45826</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>46044</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45685</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45685</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45238</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>46048</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>46050</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>46050</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46050</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>46111</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>46177</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>46052</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>46057</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>46056</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>46057</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>46178</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>46111</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>46111</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45775</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46070</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45299</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>46104</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>46182</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>46078</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>46076</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>46077</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>46077</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>46077</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>44872</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>46076</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>46073</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>46077</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>46076</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>46076</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45666</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45565</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45565</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>46189</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45519</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>46188</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>45203</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>46090</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>46190</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>46092</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>46073</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>46091</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>46073</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>46190</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>46189</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45264</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>46093</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>44790</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>46190</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>46189</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>46098</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>46196</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>46100</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>46196</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>46106</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>46077</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>46083</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>46090</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>46073</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>46198</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46076</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>46049</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>46094</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>46114</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>46199</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>46113</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45062</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>46244</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45111</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>46125</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>46126</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>46244</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45544</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45615</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45507</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>44481</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>46128</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>46203</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44460</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>46131</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>46132</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>46065</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>46131</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>45099</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>46135</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45222</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>44753</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45160</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>46069</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45076</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>46203</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>46204</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>46062</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>45544</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46035</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45525</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45617</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45238</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>46248</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>46206</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44622</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>46206</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>46206</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>46206</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>46206</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>44887</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>46162</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>46205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45212</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>44732</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>44910</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>46211</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>46254</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45610</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>46211</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45699</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45699</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>46213</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>46213</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45862</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45610</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>46259</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45554</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45757</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45544</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>46259</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>46213</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>46259</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44711</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45593</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45561</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>46261</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>45615</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>46261</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>46265</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45096</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>44711</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>46262</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45628</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45628</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45628</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>44620</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>46224</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>46224</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45301</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>46268</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46268</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>46226</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>46268</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>46272</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45782</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>44985</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45301</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45561</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>46272</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>46273</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>46227</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>45687</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>46232</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>46111</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>46275</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>46275</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>46232</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>46232</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>46232</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>46276</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>46276</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>46276</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45440</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45575</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>46276</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45642,7 +45642,7 @@
         <v>45790</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>45790</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>46281</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>46237</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>45251</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45266</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45790</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45331</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>46282</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>46282</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45307</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45615</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>46282</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>46282</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>46282</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>46282</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>46282</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45799</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>46282</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>46281</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45800</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45043</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45810</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45056</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45699</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45812</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>45817</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45817</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45826</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45834</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45836</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45839</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45839</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45841</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45848</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45848</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45848</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>45848</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45848</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45848</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45859</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45217</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45870</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45875</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>45877</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>45881</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45376</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49178,7 +49178,7 @@
         <v>44960</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44960</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>44907</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>44498</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>44637</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45377</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45567</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>44589</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45377</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44498</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>45159</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>45315</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45699</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>45938</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45938</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45938</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45938</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45957</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45938</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>46133</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>46261</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>46258</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45492</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45705</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45609</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45490</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46041</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45705</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45646</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44867</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45672</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45882</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>46153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45832</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>46149</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44469</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>46148</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45890</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>46008</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>46008</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45351</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>46157</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>46204</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>46150</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>45128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>45219</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45592</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45709</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45040</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>46008</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>46251</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45531</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45947</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45783</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45832</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>46000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>46022</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45877</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>45219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45376</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>46089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45904</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45782</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>45937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45966</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>46128</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45987</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>45833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>46211</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45376</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44827</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>44498</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>46089</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44847</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45628</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>46027</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45960</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45966</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45966</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>46085</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>46148</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45842</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>46199</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45160</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>46206</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>46211</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>46211</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>46224</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45299</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45492</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44981</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44784</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44622</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>44742</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44629</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44473</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44727</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44469</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44466</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44564</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44477</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>44715</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44617</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44466</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44720</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44872</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44655</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44838</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44526</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44722</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>44735</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>44497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44497</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45698</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>44813</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45678</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45209</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44875</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45407</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45422</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45331</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>46024</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44887</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>46024</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45307</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45615</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>45481</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45441</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45887</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45887</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>46036</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45894</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>45896</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45800</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>46044</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45826</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45902</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>46048</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45903</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>46050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>46050</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45138</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45904</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>46050</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45793</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>46052</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45647</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>46056</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45301</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>46057</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46057</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45915</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45915</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45915</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45915</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45915</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>46063</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45923</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45043</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46070</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>46076</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>46076</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>46077</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>46077</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>46076</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46076</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>46077</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>46073</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46078</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45932</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45056</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44951</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>46091</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>46090</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>46092</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46073</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>46073</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46093</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45544</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45233</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46100</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>44622</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46077</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45947</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>46083</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45699</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>46049</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>46106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>46076</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>46073</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>46094</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46113</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45812</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45956</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45954</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>46114</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45610</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45565</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45099</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45314</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45628</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>46125</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45964</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45966</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45565</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45966</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45223</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45968</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45971</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>46131</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45974</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>46128</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>46132</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45975</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45975</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45975</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>46131</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>46065</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44831</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45980</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45610</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45986</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>45697</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45554</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45986</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45986</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45986</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>45987</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>45988</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>46069</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>45988</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45987</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45987</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46135</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45988</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45660</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45817</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45817</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45994</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45645</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45768</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45758</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45775</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45113</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>45113</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>45113</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45586</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>45950</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45477</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45252</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45999</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45239</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>46139</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45674</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45374</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45593</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45593</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>45072</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45203</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45206</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45146</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45999</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45999</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45834</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45239</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45593</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45104</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45782</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>46139</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45840</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45881</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45544</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44844</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45685</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45685</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>46008</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>46008</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>46092</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>45797</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>46008</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>46008</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>46062</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45705</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>46009</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45593</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>46044</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45091</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>46010</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>46009</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>46013</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45848</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45862</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45212</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45212</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>46035</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>46041</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>46066</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45826</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45979</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44484</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>46049</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45903</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44910</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45238</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>45736</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45111</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>46146</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>45757</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>46146</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>46147</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>44914</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>46148</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44872</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>46150</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>45135</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44753</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>44644</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>45986</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>46106</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>45544</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>46154</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45757</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>45834</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45103</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45353</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>46155</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>46155</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45099</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45836</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45222</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>46157</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>46160</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44964</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44788</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45839</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45839</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>45014</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45841</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>46161</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>46164</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>46164</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45848</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>45848</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46164</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>46163</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45848</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>44896</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>46167</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>45848</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33506,7 +33506,7 @@
         <v>45848</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45848</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33652,7 +33652,7 @@
         <v>45353</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45561</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>46167</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45152</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44790</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45859</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45030</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>46171</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45217</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>46174</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>46174</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45544</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>46174</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>46177</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45870</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>46111</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45149</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45267</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>46111</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>46111</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>45610</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46178</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>46104</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44481</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>46182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>45638</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45638</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>44620</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>46189</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>46189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>46189</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>46188</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>46190</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>46190</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45758</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>46190</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45223</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44545</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45875</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>44644</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45582</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45610</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>46196</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45877</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>46196</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>46198</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44644</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>46199</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44641</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>46203</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45881</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45159</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>46203</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>46162</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45453</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>46205</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>46204</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46206</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>46206</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46206</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45628</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>46206</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>46206</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>46211</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45615</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>46211</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>44729</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45666</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>46254</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>46213</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>46213</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>45111</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>45180</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>46213</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45688</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>45705</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>45113</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>46259</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>45862</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>46259</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>46259</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>46261</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45274</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>44711</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>46261</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45222</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>46262</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45203</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45299</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>45229</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45744</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>46265</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45306</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>44693</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>46224</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>46224</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>46268</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>46268</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>46272</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>46226</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>46268</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>46272</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46227</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>46273</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>44854</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45264</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45076</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45040</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>46276</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>46276</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>46275</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>46276</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45744</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>46111</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>46232</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>46275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>46232</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>46232</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>46232</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>46237</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>45278</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45226</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44627</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46281</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44987</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46282</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>46282</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>46282</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>46282</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>46282</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>46282</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>46282</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>46282</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>45595</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45628</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45628</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>45316</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>44545</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>46281</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>46244</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45525</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>46244</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45062</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>44987</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>46289</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>44888</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>45316</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44732</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>46290</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>46248</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>44952</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45628</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45678</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>44711</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45217</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45096</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45507</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45159</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45132</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44903</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45615</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>44467</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45303</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45301</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45411</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45593</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45610</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45062</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>44481</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45209</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45699</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>45736</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45222</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45617</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45699</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45699</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45775</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45484</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45695</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45601</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>45264</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45782</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45301</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45440</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45561</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>44985</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45687</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45575</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>45790</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45790</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45790</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45266</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45251</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44637</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>44589</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45376</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>44960</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>44960</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>44907</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>44498</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45377</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45567</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>45377</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>44498</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>45159</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>45315</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45699</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45938</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45938</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45938</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45938</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45938</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>46133</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>46261</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>46258</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45492</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45705</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45609</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45490</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46041</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45705</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45646</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44867</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45672</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45882</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>46153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45832</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>46149</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>44469</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>46148</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45890</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>46008</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>46008</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45351</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>46157</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>46204</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>46150</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>45128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>45219</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45592</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45709</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45040</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>46008</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>46251</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45531</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45947</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45783</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45832</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>46000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>46022</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45877</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>45219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45376</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>46089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45904</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45782</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>45937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45966</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>46128</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45987</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>45833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>46211</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45376</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44827</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>44498</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>46089</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44847</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45628</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>46027</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45960</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45966</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45966</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>46085</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>46148</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45842</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>46199</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45160</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>46206</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>46211</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>46211</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>46224</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45299</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45492</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44981</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44784</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44622</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>44742</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44629</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44473</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44727</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44469</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44466</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44564</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44477</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>44715</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44617</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44466</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44720</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44872</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44655</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44838</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44526</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44722</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>44735</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>44497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44497</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45698</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>44813</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45678</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45209</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44875</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45407</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45422</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45331</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>46024</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44887</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>46024</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45307</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45615</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>45481</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45441</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45887</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45887</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>46036</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45894</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>45896</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45800</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>46044</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45826</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45902</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>46048</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45903</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>46050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>46050</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45138</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45904</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>46050</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45793</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>46052</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45647</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>46056</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45301</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>46057</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46057</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45915</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45915</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45915</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45915</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45915</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>46063</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45923</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45043</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46070</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>46076</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>46076</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>46077</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>46077</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>46076</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46076</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>46077</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>46073</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46078</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45932</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45056</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44951</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>46091</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>46090</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>46092</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46073</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>46073</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46093</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45544</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45233</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46100</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>44622</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46077</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45947</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>46083</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45699</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>46049</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>46106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>46076</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>46073</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>46094</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46113</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45812</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45956</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45954</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>46114</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45610</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45565</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45099</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45314</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45628</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>46125</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45964</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45966</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45565</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45966</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45223</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45968</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45971</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>46131</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45974</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>46128</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>46132</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45975</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45975</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45975</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>46131</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>46065</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44831</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45980</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45610</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45986</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>45697</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45554</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45986</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45986</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45986</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>45987</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>45988</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>46069</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>45988</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45987</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45987</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46135</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45988</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45660</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45817</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45817</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45994</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45645</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45768</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45758</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45775</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45113</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>45113</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>45113</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45586</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>45950</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45477</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45252</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45999</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45239</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>46139</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45674</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45374</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45593</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45593</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>45072</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45203</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45206</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45146</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45999</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45999</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45834</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45239</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45593</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45104</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45782</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>46139</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45840</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45881</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45544</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44844</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45685</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45685</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>46008</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>46008</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>46092</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>45797</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>46008</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>46008</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>46062</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45705</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>46009</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45593</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>46044</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45091</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>46010</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>46009</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>46013</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45848</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45862</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45212</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45212</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>46035</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>46041</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>46066</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45826</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45979</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44484</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>46049</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45903</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44910</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45238</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>45736</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45111</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>46146</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>45757</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>46146</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>46147</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>44914</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>46148</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44872</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>46150</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>45135</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44753</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>44644</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>45986</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>46106</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>45544</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>46154</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45757</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>45834</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45103</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45353</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>46155</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>46155</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45099</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45836</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45222</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>46157</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>46160</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44964</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44788</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45839</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45839</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>45014</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45841</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>46161</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>46164</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>46164</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45848</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>45848</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46164</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>46163</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45848</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>44896</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>46167</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>45848</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33506,7 +33506,7 @@
         <v>45848</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45848</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33652,7 +33652,7 @@
         <v>45353</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45561</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>46167</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45152</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44790</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45859</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45030</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>46171</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45217</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>46174</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>46174</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45544</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>46174</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>46177</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45870</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>46111</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45149</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45267</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>46111</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>46111</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>45610</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46178</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>46104</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44481</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>46182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>45638</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45638</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>44620</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>46189</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>46189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>46189</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>46188</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>46190</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>46190</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45758</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>46190</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45223</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44545</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45875</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>44644</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45582</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45610</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>46196</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45877</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>46196</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>46198</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44644</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>46199</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44641</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>46203</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45881</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45159</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>46203</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>46162</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45453</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>46205</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>46204</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46206</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>46206</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46206</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45628</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>46206</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>46206</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>46211</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45615</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>46211</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>44729</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45666</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>46254</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>46213</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>46213</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>45111</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>45180</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>46213</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45688</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>45705</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>45113</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>46259</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>45862</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>46259</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>46259</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>46261</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45274</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>44711</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>46261</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45222</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>46262</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45203</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45299</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>45229</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45744</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>46265</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45306</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>44693</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>46224</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>46224</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>46268</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>46268</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>46272</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>46226</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>46268</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>46272</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46227</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>46273</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>44854</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45264</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45076</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45040</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>46276</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>46276</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>46275</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>46276</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45744</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>46111</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>46232</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>46275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>46232</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>46232</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>46232</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>46237</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>45278</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45226</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44627</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46281</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44987</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46282</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>46282</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>46282</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>46282</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>46282</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>46282</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>46282</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>46282</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>45595</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45628</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45628</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>45316</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>44545</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>46281</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>46244</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45525</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>46244</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45062</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>44987</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>46289</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>44888</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>45316</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44732</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>46290</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>46248</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>44952</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45628</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45678</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>44711</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45217</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45096</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45507</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45159</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45132</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44903</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45615</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>44467</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45303</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45301</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45411</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45593</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45610</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45062</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>44481</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45209</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45699</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>45736</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45222</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45617</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45699</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45699</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45775</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45484</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45695</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45601</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>45264</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45782</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45301</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45440</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45561</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>44985</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45687</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45575</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>45790</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45790</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45790</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45266</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45251</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44637</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>44589</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45376</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>44960</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>44960</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>44907</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>44498</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45377</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45567</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>45377</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>44498</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>45159</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>45315</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45699</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45938</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45938</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45938</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45938</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45938</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>46133</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>46261</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>46258</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45492</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45705</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45609</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45490</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46041</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45705</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45646</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45882</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44867</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45672</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>46153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45219</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45832</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>46259</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46148</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>45890</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>46008</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>46008</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45351</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>46157</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>46204</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>45974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>46008</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>46150</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45219</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>45592</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45709</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>45040</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45159</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>46008</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>46268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>46251</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45947</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45783</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45901</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>46000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>46022</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45877</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45376</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>46089</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45904</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45782</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>45966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>46128</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45833</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>46211</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>45987</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>45376</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>44827</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44498</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>46089</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44620</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44847</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45299</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>46027</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>45960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45966</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45966</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45842</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45492</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>46148</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>46199</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>46211</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>46211</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>46224</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>45160</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>46293</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44981</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>46296</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45628</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44784</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>44623</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>44622</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44742</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>44629</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44473</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44496</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44727</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>44564</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44477</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44715</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44617</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44655</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44838</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44526</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44722</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44735</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44497</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44497</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44481</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44729</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45212</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44545</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45229</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45314</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44888</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45484</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45575</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45595</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45306</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45736</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45757</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45790</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45790</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46009</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>46008</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45209</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>46008</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>46008</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46009</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>46010</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>44903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>46013</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45266</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45887</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45353</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>44987</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44952</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46024</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45894</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>46024</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45894</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44896</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45896</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45790</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45331</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45903</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45902</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>46036</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45904</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45793</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>46042</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45307</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45615</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>46044</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45826</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>46044</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45758</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45915</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45915</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45915</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>46048</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45441</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>46050</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45800</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46050</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>45043</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45222</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45264</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45923</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45274</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>46052</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45810</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>46057</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45407</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>46056</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>46057</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>46063</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45932</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45132</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>46070</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45099</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45223</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45477</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45056</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45610</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>46078</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>46076</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>46077</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>46077</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>46077</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>46076</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>46073</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>46077</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>46076</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>46076</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45947</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45950</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45601</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45062</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44987</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>45744</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45954</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44854</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45699</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45812</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45956</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>46090</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>46092</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46073</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45960</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>46091</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45964</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>46073</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45678</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45226</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>46093</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45817</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>44844</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45223</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45966</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45966</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45968</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45817</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45971</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46098</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45971</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46100</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44951</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45267</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45223</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45975</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45975</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44788</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45975</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44985</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>46106</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45301</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>46077</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45030</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>46083</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45980</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>46090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>46073</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45233</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>46076</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>44644</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45316</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45986</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45987</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45986</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45987</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45986</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>46114</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45135</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45986</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45481</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45987</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46113</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45159</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45988</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45422</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45988</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45222</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46125</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>44545</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44914</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45593</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45239</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45826</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45999</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45834</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45374</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45999</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45586</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45239</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45072</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45146</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>45203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45593</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45674</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45113</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45113</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45113</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45999</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44693</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45593</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45252</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45950</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45647</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>46128</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45138</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45705</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45152</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>46131</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>46132</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45698</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>46065</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>46131</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>46135</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44644</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45091</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44644</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45353</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>45834</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45160</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>46069</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45836</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>46062</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45744</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45839</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45839</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46035</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45841</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45697</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>46066</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45660</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45782</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45775</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45848</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45848</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45736</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>45848</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>45848</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>45848</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45848</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45593</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45278</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46139</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45645</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45840</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45209</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>46139</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44831</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45103</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45862</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45768</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45628</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>45859</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46092</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46049</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45411</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46044</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45797</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45848</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>45217</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45903</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33543,7 +33543,7 @@
         <v>46041</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>44484</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45316</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45870</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45628</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45758</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45979</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>46146</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46146</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>46148</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>46150</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45217</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45986</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>44875</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>46155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>45699</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45544</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>46154</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>46155</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>46106</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>46157</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>45875</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45544</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45040</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>46161</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46160</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45610</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>46163</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45877</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46167</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46167</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>46164</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46164</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>46164</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45695</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45180</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>44627</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45537</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46174</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>46171</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>46174</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45881</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46174</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46111</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>46177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45887</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45610</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>46178</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>46111</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>46111</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>46104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>46182</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45303</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>46189</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46188</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>45453</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>46190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>46190</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46189</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>46190</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>45113</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>46189</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45111</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45014</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45688</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>45678</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>46196</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46196</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>44917</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46198</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>46199</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44641</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44813</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>46203</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>46203</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>46204</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>46206</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>46206</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46206</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>46206</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>46206</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46162</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>46205</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45638</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45638</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>46211</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>46211</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>46213</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>46213</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45862</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45685</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45685</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45238</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>46259</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>46213</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>46259</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46261</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46261</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>46265</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>46224</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45775</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>46224</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45299</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>46268</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>46268</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>46226</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>46272</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44872</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>46272</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45666</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>46273</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>46227</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>45565</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45565</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>46232</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>46111</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>46275</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>46275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>46232</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>46232</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>46232</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>46276</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>46276</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>46276</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45519</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>46281</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>46237</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45203</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>46282</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>46282</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45264</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>44790</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>46282</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>46282</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>46282</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>46282</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>46282</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46282</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>46281</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45062</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>46289</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45111</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45544</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45615</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45507</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>44481</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45099</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46248</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>46290</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45222</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44753</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>46295</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45076</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>46294</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>46294</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>46295</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>46295</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>46294</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>45544</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45525</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45617</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44622</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46244</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>46244</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>46147</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45988</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>46297</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>46254</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>44887</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45212</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>44732</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>44910</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45610</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45699</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45699</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45610</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>45554</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>45757</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45544</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47322,7 +47322,7 @@
         <v>44711</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45593</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45561</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45615</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45096</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>44711</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45628</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45628</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45628</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>44620</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45301</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>45782</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>44985</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>45301</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48359,7 +48359,7 @@
         <v>45561</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45687</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45440</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45376</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44960</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>44960</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44907</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>44498</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>44637</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45377</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45567</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>44589</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45377</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>44498</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45159</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45315</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45699</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>45938</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45938</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>45938</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45938</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45957</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45938</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>46133</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>46261</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>46258</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45492</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45705</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45609</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45490</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46041</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45705</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45646</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45882</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44867</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45672</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>46153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45219</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45832</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>46259</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46148</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>45890</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>46008</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>46008</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45351</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>46157</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>46204</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>45974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>46008</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>46150</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45219</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>45592</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45709</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>45040</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45159</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>46008</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>46268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>46251</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45947</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45783</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45901</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>46000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>46022</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45877</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45376</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>46089</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45904</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45782</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>45966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>46128</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45833</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>46211</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>45987</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>45376</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>44827</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44498</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>46089</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44620</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44847</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45299</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>46027</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>45960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45966</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45966</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45842</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45492</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>46148</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>46199</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>46211</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>46211</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>46224</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>45160</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>46293</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44981</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>46296</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45628</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44784</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>44623</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>44622</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44742</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>44629</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44473</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44496</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44727</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>44564</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44477</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44715</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44617</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44655</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44838</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44526</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44722</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44735</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44497</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44497</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44481</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44729</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45212</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44545</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45229</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45314</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44888</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45484</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45575</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45595</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45306</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45736</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45757</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45790</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45790</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46009</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>46008</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45209</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>46008</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>46008</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46009</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>46010</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>44903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>46013</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45266</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45887</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45353</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>44987</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44952</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46024</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45894</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>46024</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45894</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44896</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45896</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45790</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45331</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45903</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45902</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>46036</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45904</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45793</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>46042</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45307</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45615</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>46044</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45826</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>46044</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45758</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45915</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45915</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45915</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>46048</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45441</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>46050</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45800</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46050</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>45043</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45222</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45264</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45923</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45274</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>46052</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45810</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>46057</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45407</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>46056</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>46057</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>46063</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45932</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45132</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>46070</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45099</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45223</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45477</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45056</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45610</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>46078</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>46076</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>46077</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>46077</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>46077</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>46076</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>46073</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>46077</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>46076</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>46076</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45947</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45950</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45601</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45062</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44987</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>45744</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45954</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44854</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45699</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45812</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45956</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>46090</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>46092</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46073</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45960</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>46091</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45964</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>46073</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45678</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45226</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>46093</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45817</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>44844</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45223</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45966</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45966</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45968</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45817</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45971</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46098</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45971</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46100</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44951</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45267</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45223</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45975</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45975</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44788</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45975</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44985</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>46106</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45301</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>46077</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45030</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>46083</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45980</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>46090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>46073</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45233</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>46076</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>44644</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45316</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45986</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45987</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45986</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45987</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45986</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>46114</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45135</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45986</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45481</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45987</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46113</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45159</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45988</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45422</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45988</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45222</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46125</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>44545</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44914</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45593</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45239</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45826</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45999</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45834</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45374</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45999</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45586</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45239</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45072</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45146</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>45203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45593</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45674</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45113</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45113</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45113</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45999</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44693</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45593</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45252</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45950</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45647</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>46128</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45138</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45705</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45152</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>46131</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>46132</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45698</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>46065</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>46131</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>46135</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44644</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45091</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44644</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45353</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>45834</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45160</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>46069</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45836</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>46062</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45744</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45839</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45839</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46035</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45841</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45697</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>46066</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45660</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45782</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45775</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45848</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45848</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45736</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>45848</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>45848</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>45848</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45848</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45593</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45278</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46139</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45645</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45840</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45209</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>46139</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44831</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45103</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45862</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45768</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45628</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>45859</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46092</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46049</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45411</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46044</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45797</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45848</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>45217</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45903</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33543,7 +33543,7 @@
         <v>46041</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>44484</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45316</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45870</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45628</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45758</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45979</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>46146</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46146</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>46148</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>46150</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45217</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45986</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>44875</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>46155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>45699</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45544</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>46154</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>46155</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>46106</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>46157</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>45875</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45544</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45040</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>46161</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46160</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45610</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>46163</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45877</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46167</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46167</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>46164</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46164</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>46164</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45695</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45180</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>44627</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45537</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46174</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>46171</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>46174</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45881</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46174</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46111</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>46177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45887</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45610</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>46178</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>46111</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>46111</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>46104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>46182</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45303</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>46189</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46188</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>45453</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>46190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>46190</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46189</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>46190</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>45113</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>46189</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45111</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45014</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45688</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>45678</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>46196</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46196</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>44917</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46198</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>46199</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44641</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44813</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>46203</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>46203</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>46204</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>46206</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>46206</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46206</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>46206</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>46206</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46162</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>46205</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45638</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45638</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>46211</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>46211</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>46213</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>46213</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45862</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45685</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45685</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45238</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>46259</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>46213</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>46259</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46261</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46261</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>46265</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>46224</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45775</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>46224</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45299</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>46268</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>46268</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>46226</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>46272</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44872</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>46272</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45666</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>46273</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>46227</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>45565</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45565</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>46232</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>46111</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>46275</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>46275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>46232</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>46232</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>46232</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>46276</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>46276</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>46276</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45519</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>46281</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>46237</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45203</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>46282</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>46282</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45264</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>44790</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>46282</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>46282</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>46282</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>46282</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>46282</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46282</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>46281</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45062</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>46289</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45111</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45544</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45615</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45507</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>44481</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45099</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46248</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>46290</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45222</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44753</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>46295</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45076</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>46294</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>46294</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>46295</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>46295</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>46294</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>45544</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45525</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45617</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44622</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46244</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>46244</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>46147</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45988</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>46297</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>46254</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>44887</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45212</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>44732</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>44910</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45610</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45699</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45699</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45610</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>45554</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>45757</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45544</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47322,7 +47322,7 @@
         <v>44711</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45593</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45561</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45615</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45096</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>44711</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45628</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45628</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45628</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>44620</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45301</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>45782</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>44985</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>45301</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48359,7 +48359,7 @@
         <v>45561</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45687</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45440</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45376</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44960</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>44960</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44907</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>44498</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>44637</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45377</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45567</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>44589</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45377</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>44498</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45159</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45315</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45699</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>45938</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45938</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>45938</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45938</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45957</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45938</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>46133</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>46261</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>46258</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45492</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45609</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45705</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>46041</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45705</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45646</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45832</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45672</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>44867</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>45219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>45832</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>46259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45939</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>46149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>46148</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>46239</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45890</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>44714</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>45351</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>46008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>46157</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46204</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>46150</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>45219</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>46030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45159</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45040</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45709</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45592</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>46008</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>46268</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>46251</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>45947</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45901</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45877</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>46000</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44858</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>46022</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>46303</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>46303</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>46303</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45376</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>46089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45782</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>45937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45966</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>46128</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45833</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>46211</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45376</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>44827</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44498</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>46089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44620</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>45628</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>44981</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>45903</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45160</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45960</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45966</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45842</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45299</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45492</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>46027</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>46085</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>46148</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>46199</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>46206</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>46211</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>46211</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>46224</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46293</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>46296</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44623</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>44622</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44742</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>44629</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>44496</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>44727</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>44543</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44617</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44655</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44715</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44526</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44838</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44720</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44722</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44735</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44872</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45209</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>44497</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44497</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45135</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45132</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44753</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44644</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44875</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45757</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44813</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45407</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44903</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45422</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45615</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45678</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45103</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45303</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45353</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45099</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45222</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45698</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>44964</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44788</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>45014</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>45223</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45301</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45411</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45593</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45610</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45062</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>44896</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>44481</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45353</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45561</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45209</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45152</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44887</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>44790</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45537</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45887</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45887</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45699</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45030</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45222</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45544</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45481</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45544</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45441</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45894</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45894</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45896</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45617</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>45902</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45699</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45699</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45775</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45484</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45903</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45695</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>45601</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45904</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45264</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45793</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45149</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45267</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45782</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45138</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45610</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45915</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45915</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45301</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45647</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45440</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45561</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45915</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>44985</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44481</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45915</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45638</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45638</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45519</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45687</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45575</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45301</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>44620</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45923</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45790</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45790</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45758</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45790</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45266</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45223</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44545</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44644</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45582</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45251</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>45610</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45331</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44917</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45244</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45307</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45615</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>44644</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45932</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44951</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44641</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45159</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45800</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45453</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45544</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45233</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45043</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44622</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45628</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45056</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45810</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45699</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45812</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45615</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44729</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45666</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45817</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45817</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45610</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45565</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45111</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45180</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45099</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45950</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>45314</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45688</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45947</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>45628</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45705</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45565</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45826</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45113</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45956</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45954</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>45960</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44711</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>45834</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45836</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45222</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45964</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45966</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44831</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45839</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45966</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45839</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45610</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45841</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45697</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45554</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45223</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45968</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45203</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45299</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45971</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45848</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45848</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45848</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45229</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45238</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45974</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45848</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45848</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45744</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45848</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>45974</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45306</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>44985</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44693</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45113</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45477</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45859</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45975</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>45217</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>45975</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45870</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45975</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45544</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44844</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45685</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45685</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44854</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45091</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45980</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45875</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45264</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>45877</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45076</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>45040</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45212</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45212</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45744</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45881</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45278</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>45226</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>46098</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45986</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45986</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>46100</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44627</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45986</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45986</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45986</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>46077</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44987</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>46083</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44910</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45987</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>46049</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45988</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>46106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45595</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45238</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>46076</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>46073</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45736</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45111</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>46090</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>46094</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45987</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45987</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45988</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>46113</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45757</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>45628</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45628</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45316</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45994</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44914</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>46114</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>44545</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>46125</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45113</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45113</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45586</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45950</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45252</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45999</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45239</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45674</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45374</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45593</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45593</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45072</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45203</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45206</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45146</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45999</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45999</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45834</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>45239</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45104</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>46131</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>46128</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>46132</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45525</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>46131</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>46065</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>46008</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45062</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>46008</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46069</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44987</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44888</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46135</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>46008</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46008</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45316</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46009</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45660</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>46009</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>46013</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44732</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45645</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45768</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45758</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>46024</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45775</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>46024</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>46139</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45782</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44952</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45160</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>46139</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45840</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45881</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45628</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>46036</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>46092</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45797</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46062</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45678</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>44711</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45593</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>46044</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>46042</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45217</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45096</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45848</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>46044</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45862</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>46044</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>46035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45507</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45826</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>46041</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>46048</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>46066</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45979</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>46050</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>44484</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>46050</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>46049</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>46052</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45903</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>46056</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>46057</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46057</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46146</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46146</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>46063</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46148</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>46150</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>46070</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45986</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>46106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>46076</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>46076</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>46077</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45544</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>46077</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>46076</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>46077</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>46154</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>46076</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>46077</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>46073</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>46078</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>46155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>46157</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>46091</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>46090</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>46160</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>46092</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>46073</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>46073</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>46093</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>46161</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>46163</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>46164</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>46164</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>46164</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>46163</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>46167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>46167</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>46171</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>46174</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>46174</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46174</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46177</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46111</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46111</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>46178</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>46104</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>46182</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>46189</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>46189</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>46189</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>46188</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>46190</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>46190</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>46190</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>46196</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>46196</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>46198</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>46199</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46203</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>46162</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46205</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>46204</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>46206</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>46206</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>46206</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>46206</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>46206</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>46211</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>46211</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>46213</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>46213</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>46213</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45862</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46265</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>46224</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>46224</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>46268</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>46268</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>46272</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45423,7 +45423,7 @@
         <v>46226</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>46272</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46227</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>46273</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>46276</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>46276</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>46275</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46276</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>46111</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>46232</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>46275</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>46232</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>46232</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>46237</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>46281</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>46282</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>46282</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>46282</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>46282</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>46282</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>46282</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>46282</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46282</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46281</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46289</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46248</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46294</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>46294</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>46294</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>46295</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46295</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>46295</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>46297</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>46244</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46244</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45988</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>46147</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>46300</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46290</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>46232</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46254</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>46302</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>46259</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>46259</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>46302</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46301</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>46261</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>46303</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46261</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>46303</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>46303</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>44637</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>44589</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49422,7 +49422,7 @@
         <v>45376</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>44960</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>44960</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>44907</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>44498</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45377</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>45567</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45377</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>44498</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45159</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>45315</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45699</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50338,7 +50338,7 @@
         <v>45938</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45938</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45938</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50572,7 +50572,7 @@
         <v>45938</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45938</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>45957</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50801,7 +50801,7 @@
         <v>46133</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>46258</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>46261</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45492</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45609</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45705</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>46041</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45705</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45646</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45832</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45672</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>44867</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>45219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>45832</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>46259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45939</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>46149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>46148</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>46239</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45890</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>44714</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>45351</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>46008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>46157</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46204</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>46150</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>46008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>45219</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>46030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45159</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45040</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45709</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45592</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>46008</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>46268</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>46251</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>45947</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45901</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45877</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>46000</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44858</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>46022</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>46303</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>46303</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>46303</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45376</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>46089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45782</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>45937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45966</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>46128</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45833</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>46211</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45376</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>44827</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44498</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>46089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44620</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>45628</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>44981</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>45903</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45160</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45960</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45966</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45842</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45299</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45492</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>46027</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>46085</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>46148</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>46199</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>46206</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>46211</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>46211</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>46224</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46293</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>46296</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44784</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44623</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>44622</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44742</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>44629</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>44496</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>44727</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>44543</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44617</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44655</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44715</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44526</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44838</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44720</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44722</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44735</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44872</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45209</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>44497</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44497</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45135</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45132</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44753</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44644</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44875</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45757</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44813</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45407</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44903</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45422</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45615</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45678</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45103</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45303</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45353</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45099</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45222</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45698</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>44964</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44788</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>45014</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>45223</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45301</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45411</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45593</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45610</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45062</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>44896</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>44481</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45353</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45561</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45209</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45152</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44887</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>44790</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45537</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45887</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45887</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45699</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45030</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45222</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45544</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45481</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45544</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45441</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45894</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45894</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45896</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45617</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>45902</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45699</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45699</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45775</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45484</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45903</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45695</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>45601</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45904</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45264</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45793</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45149</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45267</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45782</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45138</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45610</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45915</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45915</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45301</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45647</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45440</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45561</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45915</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>44985</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44481</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45915</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45638</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45638</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45519</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45687</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45575</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45301</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>44620</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45923</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45790</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45790</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45758</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45790</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45266</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45223</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44545</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44644</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45582</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45251</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>45610</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45331</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44917</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45244</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45307</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45615</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>44644</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45932</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44951</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44641</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45159</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45800</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45453</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45544</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45233</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45043</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44622</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45628</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45056</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45810</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45699</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45812</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45615</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44729</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45666</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45817</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45817</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45610</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45565</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45111</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45180</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45099</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45950</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>45314</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45688</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45947</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>45628</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45705</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45565</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45826</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45113</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45956</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45954</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>45960</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44711</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>45834</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45836</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45222</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45964</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45966</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44831</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45839</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45966</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45839</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45610</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45841</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45697</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45554</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45223</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45968</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45203</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45299</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45971</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45848</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45848</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45848</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45229</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45238</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45974</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45848</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45848</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45744</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45848</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>45974</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45306</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>44985</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44693</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45113</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45477</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45859</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45975</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>45217</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>45975</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45870</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45975</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45544</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44844</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45685</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45685</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44854</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45091</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45980</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45875</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45264</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>45877</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45076</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>45040</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45212</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45212</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45744</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45881</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45278</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>45226</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>46098</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45986</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45986</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>46100</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44627</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45986</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45986</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45986</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>46077</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44987</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>46083</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44910</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45987</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>46049</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45988</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>46106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45595</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45238</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>46076</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>46073</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45736</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45111</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>46090</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>46094</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45987</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45987</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45988</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>46113</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45757</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>45628</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45628</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45316</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45994</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44914</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>46114</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>44545</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>46125</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45113</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45113</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45586</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45950</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45252</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45999</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45239</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45674</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45374</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45593</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45593</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45072</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45203</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45206</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45146</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45999</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45999</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45834</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>45239</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45104</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>46131</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>46128</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>46132</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45525</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>46131</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>46065</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>46008</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45062</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>46008</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46069</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44987</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44888</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46135</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>46008</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46008</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45316</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46009</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45660</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>46009</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>46013</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44732</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45645</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45768</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45758</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>46024</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45775</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>46024</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>46139</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45782</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44952</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45160</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>46139</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45840</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45881</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45628</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>46036</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>46092</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45797</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46062</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45678</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>44711</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45593</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>46044</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>46042</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45217</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45096</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45848</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>46044</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45862</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>46044</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>46035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45507</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45826</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>46041</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>46048</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>46066</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45979</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>46050</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>44484</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>46050</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>46049</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>46052</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45903</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>46056</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>46057</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46057</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46146</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46146</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>46063</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46148</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>46150</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>46070</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45986</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>46106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>46076</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>46076</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>46077</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45544</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>46077</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>46076</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>46077</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>46154</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>46076</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>46077</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>46073</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>46078</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>46155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>46157</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>46091</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>46090</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>46160</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>46092</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>46073</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>46073</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>46093</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>46161</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>46163</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>46164</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>46164</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>46164</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>46163</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>46167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>46167</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>46171</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>46174</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>46174</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46174</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46177</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46111</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46111</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>46178</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>46104</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>46182</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>46189</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>46189</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>46189</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>46188</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>46190</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>46190</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>46190</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>46196</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>46196</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>46198</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>46199</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46203</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>46162</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46205</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>46204</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>46206</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>46206</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>46206</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>46206</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>46206</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>46211</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>46211</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>46213</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>46213</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>46213</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45862</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46265</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>46224</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>46224</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>46268</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>46268</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>46272</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45423,7 +45423,7 @@
         <v>46226</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>46272</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46227</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>46273</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>46276</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>46276</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>46275</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46276</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>46111</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>46232</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>46275</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>46232</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>46232</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>46237</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>46281</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>46282</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>46282</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>46282</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>46282</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>46282</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>46282</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>46282</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46282</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46281</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46289</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46248</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46294</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>46294</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>46294</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>46295</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46295</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>46295</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>46297</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>46244</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46244</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45988</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>46147</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>46300</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46290</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>46232</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46254</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>46302</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>46259</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>46259</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>46302</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46301</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>46261</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>46303</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46261</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>46303</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>46303</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>44637</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>44589</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49422,7 +49422,7 @@
         <v>45376</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>44960</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>44960</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>44907</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>44498</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45377</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>45567</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45377</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>44498</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45159</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>45315</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45699</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50338,7 +50338,7 @@
         <v>45938</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45938</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45938</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50572,7 +50572,7 @@
         <v>45938</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45938</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>45957</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50801,7 +50801,7 @@
         <v>46133</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>46258</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>46261</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
         <v>20</v>
@@ -805,13 +805,13 @@
         <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T3" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="U3" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -841,12 +841,14 @@
 Vaxspindling
 Vedskivlav
 Violettgrå tagellav
+Björksplintborre
 Bronshjon
 Gullgröppa
 Mindre märgborre
 Rävticka
 Tibast
-Vågbandad barkbock</t>
+Vågbandad barkbock
+Kärrfibbla</t>
         </is>
       </c>
       <c r="W3">
@@ -906,7 +908,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1050,7 +1052,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1192,7 +1194,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1335,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1469,7 +1471,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1614,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1750,7 +1752,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1892,7 +1894,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2028,7 +2030,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2164,7 +2166,7 @@
         <v>45492</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2297,7 +2299,7 @@
         <v>45204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2430,7 +2432,7 @@
         <v>45705</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2560,7 +2562,7 @@
         <v>45609</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2686,7 +2688,7 @@
         <v>45490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2810,7 +2812,7 @@
         <v>46041</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2934,7 +2936,7 @@
         <v>45705</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3061,7 +3063,7 @@
         <v>45646</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3188,7 +3190,7 @@
         <v>45832</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3310,7 +3312,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3432,7 +3434,7 @@
         <v>44867</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3559,7 +3561,7 @@
         <v>45672</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3681,7 +3683,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3812,7 +3814,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3935,7 @@
         <v>45219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4052,7 +4054,7 @@
         <v>45832</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4171,7 +4173,7 @@
         <v>46259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4295,7 +4297,7 @@
         <v>46149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4418,7 +4420,7 @@
         <v>45939</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4541,7 +4543,7 @@
         <v>46148</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4658,7 +4660,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4780,7 +4782,7 @@
         <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4902,7 +4904,7 @@
         <v>46239</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5024,7 +5026,7 @@
         <v>45890</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5140,7 +5142,7 @@
         <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5258,7 @@
         <v>46268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5377,7 +5379,7 @@
         <v>44714</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5497,7 +5499,7 @@
         <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5612,7 +5614,7 @@
         <v>45159</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5732,7 +5734,7 @@
         <v>45351</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5847,7 +5849,7 @@
         <v>45300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5962,7 +5964,7 @@
         <v>46157</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6076,7 +6078,7 @@
         <v>46204</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6186,7 +6188,7 @@
         <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6305,7 +6307,7 @@
         <v>46008</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6419,7 +6421,7 @@
         <v>46150</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6533,7 +6535,7 @@
         <v>45785</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6652,7 +6654,7 @@
         <v>45974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6770,7 +6772,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6889,7 +6891,7 @@
         <v>45128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7007,7 +7009,7 @@
         <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7120,7 +7122,7 @@
         <v>46030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7229,7 +7231,7 @@
         <v>45709</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7341,7 +7343,7 @@
         <v>45040</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7449,7 +7451,7 @@
         <v>45592</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7561,7 +7563,7 @@
         <v>46008</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7673,7 +7675,7 @@
         <v>46251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7786,7 +7788,7 @@
         <v>45531</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7898,7 +7900,7 @@
         <v>45783</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8010,7 +8012,7 @@
         <v>45947</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8122,7 +8124,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8229,7 +8231,7 @@
         <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8340,7 +8342,7 @@
         <v>45901</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8452,7 +8454,7 @@
         <v>46022</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8563,7 +8565,7 @@
         <v>46000</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8670,7 +8672,7 @@
         <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8781,7 +8783,7 @@
         <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8888,7 +8890,7 @@
         <v>46303</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8999,7 +9001,7 @@
         <v>46303</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9110,7 +9112,7 @@
         <v>46303</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9221,7 +9223,7 @@
         <v>45877</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9333,7 +9335,7 @@
         <v>45376</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9449,7 +9451,7 @@
         <v>46089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9569,7 +9571,7 @@
         <v>45833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9679,7 +9681,7 @@
         <v>45904</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9789,7 +9791,7 @@
         <v>45937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9904,7 +9906,7 @@
         <v>45966</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10019,7 +10021,7 @@
         <v>44509</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10125,7 +10127,7 @@
         <v>46128</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10235,7 +10237,7 @@
         <v>46211</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10346,7 +10348,7 @@
         <v>45987</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10456,7 +10458,7 @@
         <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10571,7 +10573,7 @@
         <v>45376</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10682,7 +10684,7 @@
         <v>44827</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10793,7 +10795,7 @@
         <v>44498</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10904,7 +10906,7 @@
         <v>46089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11019,7 +11021,7 @@
         <v>44620</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11124,7 +11126,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11234,7 +11236,7 @@
         <v>45299</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11343,7 +11345,7 @@
         <v>45903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11448,7 +11450,7 @@
         <v>46085</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11562,7 +11564,7 @@
         <v>45492</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11672,7 +11674,7 @@
         <v>46148</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11777,7 +11779,7 @@
         <v>45960</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11891,7 +11893,7 @@
         <v>45966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12000,7 +12002,7 @@
         <v>45966</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12105,7 +12107,7 @@
         <v>46027</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12214,7 +12216,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12323,7 +12325,7 @@
         <v>46206</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12428,7 +12430,7 @@
         <v>46211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12538,7 +12540,7 @@
         <v>45160</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12648,7 +12650,7 @@
         <v>46211</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12758,7 +12760,7 @@
         <v>46224</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12868,7 +12870,7 @@
         <v>44981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12982,7 +12984,7 @@
         <v>45628</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13091,7 +13093,7 @@
         <v>46293</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13205,7 +13207,7 @@
         <v>46309</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13315,7 +13317,7 @@
         <v>46296</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13425,7 +13427,7 @@
         <v>45842</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13534,7 +13536,7 @@
         <v>44784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13612,7 +13614,7 @@
         <v>44623</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13685,7 +13687,7 @@
         <v>44622</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13758,7 +13760,7 @@
         <v>44742</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13831,7 +13833,7 @@
         <v>44629</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13904,7 +13906,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13977,7 +13979,7 @@
         <v>44727</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14055,7 +14057,7 @@
         <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14133,7 +14135,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14211,7 +14213,7 @@
         <v>44715</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14284,7 +14286,7 @@
         <v>44617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14362,7 +14364,7 @@
         <v>44720</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14435,7 +14437,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14508,7 +14510,7 @@
         <v>44655</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14581,7 +14583,7 @@
         <v>44838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14654,7 +14656,7 @@
         <v>44526</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14732,7 +14734,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14810,7 +14812,7 @@
         <v>44735</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14888,7 +14890,7 @@
         <v>44497</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14961,7 +14963,7 @@
         <v>44497</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15034,7 +15036,7 @@
         <v>45212</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15107,7 +15109,7 @@
         <v>44729</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15185,7 +15187,7 @@
         <v>44545</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15258,7 +15260,7 @@
         <v>44888</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15331,7 +15333,7 @@
         <v>45229</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15409,7 +15411,7 @@
         <v>45484</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15482,7 +15484,7 @@
         <v>45595</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15555,7 +15557,7 @@
         <v>45314</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15633,7 +15635,7 @@
         <v>45306</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15706,7 +15708,7 @@
         <v>45757</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15779,7 +15781,7 @@
         <v>45209</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15857,7 +15859,7 @@
         <v>45736</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15935,7 +15937,7 @@
         <v>45582</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16013,7 +16015,7 @@
         <v>45353</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16086,7 +16088,7 @@
         <v>44903</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16164,7 +16166,7 @@
         <v>44987</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16237,7 +16239,7 @@
         <v>44952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16310,7 +16312,7 @@
         <v>44896</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16388,7 +16390,7 @@
         <v>45758</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16461,7 +16463,7 @@
         <v>45222</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16534,7 +16536,7 @@
         <v>45244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16607,7 +16609,7 @@
         <v>45441</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16680,7 +16682,7 @@
         <v>45264</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16753,7 +16755,7 @@
         <v>45274</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16826,7 +16828,7 @@
         <v>45407</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16899,7 +16901,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16977,7 +16979,7 @@
         <v>45132</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17050,7 +17052,7 @@
         <v>45223</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17123,7 +17125,7 @@
         <v>45610</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17196,7 +17198,7 @@
         <v>45477</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17274,7 +17276,7 @@
         <v>45601</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17347,7 +17349,7 @@
         <v>45062</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17420,7 +17422,7 @@
         <v>44987</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17493,7 +17495,7 @@
         <v>45744</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17571,7 +17573,7 @@
         <v>44854</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17649,7 +17651,7 @@
         <v>45149</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17727,7 +17729,7 @@
         <v>45678</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17800,7 +17802,7 @@
         <v>45226</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17873,7 +17875,7 @@
         <v>44844</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17946,7 +17948,7 @@
         <v>45267</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18019,7 +18021,7 @@
         <v>45223</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18092,7 +18094,7 @@
         <v>44951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18165,7 +18167,7 @@
         <v>44985</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18238,7 +18240,7 @@
         <v>44788</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18316,7 +18318,7 @@
         <v>45301</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18389,7 +18391,7 @@
         <v>45030</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18462,7 +18464,7 @@
         <v>44644</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18535,7 +18537,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18608,7 +18610,7 @@
         <v>45233</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18686,7 +18688,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18759,7 +18761,7 @@
         <v>45660</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18837,7 +18839,7 @@
         <v>45135</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18910,7 +18912,7 @@
         <v>45481</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18988,7 +18990,7 @@
         <v>45782</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19066,7 +19068,7 @@
         <v>45775</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19139,7 +19141,7 @@
         <v>45159</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19212,7 +19214,7 @@
         <v>45422</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19285,7 +19287,7 @@
         <v>45593</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19358,7 +19360,7 @@
         <v>46139</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19436,7 +19438,7 @@
         <v>45222</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19509,7 +19511,7 @@
         <v>45887</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19582,7 +19584,7 @@
         <v>44545</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19655,7 +19657,7 @@
         <v>45645</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19728,7 +19730,7 @@
         <v>45887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19801,7 +19803,7 @@
         <v>45840</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19874,7 +19876,7 @@
         <v>44914</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19947,7 +19949,7 @@
         <v>46139</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20025,7 +20027,7 @@
         <v>45705</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20098,7 +20100,7 @@
         <v>44693</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20171,7 +20173,7 @@
         <v>45647</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20244,7 +20246,7 @@
         <v>45138</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20322,7 +20324,7 @@
         <v>45894</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20400,7 +20402,7 @@
         <v>45705</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20473,7 +20475,7 @@
         <v>45894</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20551,7 +20553,7 @@
         <v>45152</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20629,7 +20631,7 @@
         <v>45896</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20707,7 +20709,7 @@
         <v>45698</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20780,7 +20782,7 @@
         <v>45862</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20853,7 +20855,7 @@
         <v>45768</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20931,7 +20933,7 @@
         <v>44644</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21004,7 +21006,7 @@
         <v>46092</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21077,7 +21079,7 @@
         <v>46049</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21150,7 +21152,7 @@
         <v>45091</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21223,7 +21225,7 @@
         <v>46044</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21296,7 +21298,7 @@
         <v>45797</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21369,7 +21371,7 @@
         <v>44644</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21442,7 +21444,7 @@
         <v>45848</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21515,7 +21517,7 @@
         <v>45353</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21588,7 +21590,7 @@
         <v>45903</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21661,7 +21663,7 @@
         <v>46041</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21734,7 +21736,7 @@
         <v>45903</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21807,7 +21809,7 @@
         <v>45902</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21880,7 +21882,7 @@
         <v>45904</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21958,7 +21960,7 @@
         <v>45758</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22031,7 +22033,7 @@
         <v>45979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22104,7 +22106,7 @@
         <v>45881</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22177,7 +22179,7 @@
         <v>45793</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22250,7 +22252,7 @@
         <v>45744</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22328,7 +22330,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22406,7 +22408,7 @@
         <v>45915</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22484,7 +22486,7 @@
         <v>45915</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22562,7 +22564,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22640,7 +22642,7 @@
         <v>45915</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22718,7 +22720,7 @@
         <v>46146</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22791,7 +22793,7 @@
         <v>45697</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22864,7 +22866,7 @@
         <v>46146</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22937,7 +22939,7 @@
         <v>45923</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23015,7 +23017,7 @@
         <v>45736</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23093,7 +23095,7 @@
         <v>46148</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23171,7 +23173,7 @@
         <v>45278</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23244,7 +23246,7 @@
         <v>46150</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23322,7 +23324,7 @@
         <v>45932</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23395,7 +23397,7 @@
         <v>45209</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23473,7 +23475,7 @@
         <v>44831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23546,7 +23548,7 @@
         <v>45103</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23619,7 +23621,7 @@
         <v>45986</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23692,7 +23694,7 @@
         <v>45628</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23770,7 +23772,7 @@
         <v>46155</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23848,7 +23850,7 @@
         <v>45411</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23921,7 +23923,7 @@
         <v>45947</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23994,7 +23996,7 @@
         <v>45950</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24067,7 +24069,7 @@
         <v>45544</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24145,7 +24147,7 @@
         <v>44964</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24223,7 +24225,7 @@
         <v>45954</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24296,7 +24298,7 @@
         <v>46154</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24369,7 +24371,7 @@
         <v>45956</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24442,7 +24444,7 @@
         <v>46106</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24515,7 +24517,7 @@
         <v>46157</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24593,7 +24595,7 @@
         <v>45960</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24671,7 +24673,7 @@
         <v>45964</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24744,7 +24746,7 @@
         <v>45316</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24817,7 +24819,7 @@
         <v>45628</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24895,7 +24897,7 @@
         <v>45223</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24968,7 +24970,7 @@
         <v>45966</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25041,7 +25043,7 @@
         <v>45966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25119,7 +25121,7 @@
         <v>45968</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25197,7 +25199,7 @@
         <v>46161</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25270,7 +25272,7 @@
         <v>45971</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25348,7 +25350,7 @@
         <v>46160</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25421,7 +25423,7 @@
         <v>45971</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25499,7 +25501,7 @@
         <v>46163</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25577,7 +25579,7 @@
         <v>45975</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25650,7 +25652,7 @@
         <v>45974</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25723,7 +25725,7 @@
         <v>45975</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25796,7 +25798,7 @@
         <v>45974</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25869,7 +25871,7 @@
         <v>46163</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25947,7 +25949,7 @@
         <v>45975</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26020,7 +26022,7 @@
         <v>45980</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26098,7 +26100,7 @@
         <v>45217</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26171,7 +26173,7 @@
         <v>44875</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26249,7 +26251,7 @@
         <v>45699</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26322,7 +26324,7 @@
         <v>45986</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26395,7 +26397,7 @@
         <v>45987</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26468,7 +26470,7 @@
         <v>45986</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26541,7 +26543,7 @@
         <v>45987</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26614,7 +26616,7 @@
         <v>45986</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26687,7 +26689,7 @@
         <v>46167</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26765,7 +26767,7 @@
         <v>46167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26843,7 +26845,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26916,7 +26918,7 @@
         <v>45987</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26989,7 +26991,7 @@
         <v>46164</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27067,7 +27069,7 @@
         <v>45986</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27140,7 +27142,7 @@
         <v>46164</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27218,7 +27220,7 @@
         <v>46164</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27296,7 +27298,7 @@
         <v>45988</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27369,7 +27371,7 @@
         <v>45988</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27442,7 +27444,7 @@
         <v>45544</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27515,7 +27517,7 @@
         <v>45040</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27588,7 +27590,7 @@
         <v>45610</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27666,7 +27668,7 @@
         <v>45994</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27739,7 +27741,7 @@
         <v>45593</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27812,7 +27814,7 @@
         <v>45239</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27885,7 +27887,7 @@
         <v>45999</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27958,7 +27960,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28031,7 +28033,7 @@
         <v>45374</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28104,7 +28106,7 @@
         <v>45999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28177,7 +28179,7 @@
         <v>45586</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28250,7 +28252,7 @@
         <v>45239</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28323,7 +28325,7 @@
         <v>45072</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28396,7 +28398,7 @@
         <v>45146</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28469,7 +28471,7 @@
         <v>45203</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28542,7 +28544,7 @@
         <v>45593</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28615,7 +28617,7 @@
         <v>45206</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28688,7 +28690,7 @@
         <v>45674</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28761,7 +28763,7 @@
         <v>45113</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28834,7 +28836,7 @@
         <v>45113</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28907,7 +28909,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28980,7 +28982,7 @@
         <v>45999</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29053,7 +29055,7 @@
         <v>45104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29126,7 +29128,7 @@
         <v>45593</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29199,7 +29201,7 @@
         <v>45252</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29272,7 +29274,7 @@
         <v>45950</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29345,7 +29347,7 @@
         <v>45695</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29418,7 +29420,7 @@
         <v>45113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29496,7 +29498,7 @@
         <v>46174</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29574,7 +29576,7 @@
         <v>46171</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29652,7 +29654,7 @@
         <v>45180</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29730,7 +29732,7 @@
         <v>46174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29803,7 +29805,7 @@
         <v>44627</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29876,7 +29878,7 @@
         <v>46174</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29949,7 +29951,7 @@
         <v>45537</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30022,7 +30024,7 @@
         <v>46009</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30095,7 +30097,7 @@
         <v>46008</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30168,7 +30170,7 @@
         <v>46008</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30241,7 +30243,7 @@
         <v>46008</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30314,7 +30316,7 @@
         <v>46008</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30387,7 +30389,7 @@
         <v>46009</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30460,7 +30462,7 @@
         <v>46010</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30533,7 +30535,7 @@
         <v>46013</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30606,7 +30608,7 @@
         <v>45610</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30679,7 +30681,7 @@
         <v>46024</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30752,7 +30754,7 @@
         <v>46024</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30825,7 +30827,7 @@
         <v>45303</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30898,7 +30900,7 @@
         <v>46036</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30971,7 +30973,7 @@
         <v>46111</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31049,7 +31051,7 @@
         <v>46177</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31127,7 +31129,7 @@
         <v>45453</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31200,7 +31202,7 @@
         <v>46042</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31273,7 +31275,7 @@
         <v>46178</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31351,7 +31353,7 @@
         <v>46111</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31429,7 +31431,7 @@
         <v>46044</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31502,7 +31504,7 @@
         <v>45826</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31575,7 +31577,7 @@
         <v>46044</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31648,7 +31650,7 @@
         <v>46111</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31726,7 +31728,7 @@
         <v>45113</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31804,7 +31806,7 @@
         <v>45111</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31882,7 +31884,7 @@
         <v>45014</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31955,7 +31957,7 @@
         <v>45688</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32028,7 +32030,7 @@
         <v>46048</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32101,7 +32103,7 @@
         <v>45678</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32174,7 +32176,7 @@
         <v>46050</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32247,7 +32249,7 @@
         <v>46050</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32320,7 +32322,7 @@
         <v>46104</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32393,7 +32395,7 @@
         <v>46182</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32466,7 +32468,7 @@
         <v>46052</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32539,7 +32541,7 @@
         <v>46057</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32612,7 +32614,7 @@
         <v>46056</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32685,7 +32687,7 @@
         <v>46057</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32758,7 +32760,7 @@
         <v>44917</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32836,7 +32838,7 @@
         <v>46063</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32909,7 +32911,7 @@
         <v>46189</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32982,7 +32984,7 @@
         <v>46070</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33055,7 +33057,7 @@
         <v>44641</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33128,7 +33130,7 @@
         <v>46188</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33206,7 +33208,7 @@
         <v>44813</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33279,7 +33281,7 @@
         <v>46078</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33357,7 +33359,7 @@
         <v>46076</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33430,7 +33432,7 @@
         <v>46077</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33503,7 +33505,7 @@
         <v>46077</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33581,7 +33583,7 @@
         <v>46077</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33659,7 +33661,7 @@
         <v>46076</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33732,7 +33734,7 @@
         <v>46073</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33810,7 +33812,7 @@
         <v>46077</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33883,7 +33885,7 @@
         <v>46076</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33956,7 +33958,7 @@
         <v>46076</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34029,7 +34031,7 @@
         <v>46190</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34107,7 +34109,7 @@
         <v>46190</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34180,7 +34182,7 @@
         <v>46189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34258,7 +34260,7 @@
         <v>46090</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34331,7 +34333,7 @@
         <v>45638</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34404,7 +34406,7 @@
         <v>45638</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34477,7 +34479,7 @@
         <v>46190</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34550,7 +34552,7 @@
         <v>46092</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34623,7 +34625,7 @@
         <v>46073</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34701,7 +34703,7 @@
         <v>46189</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34774,7 +34776,7 @@
         <v>46091</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34852,7 +34854,7 @@
         <v>46073</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34930,7 +34932,7 @@
         <v>46093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35008,7 +35010,7 @@
         <v>45685</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35081,7 +35083,7 @@
         <v>45685</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35154,7 +35156,7 @@
         <v>46098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35227,7 +35229,7 @@
         <v>45238</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35300,7 +35302,7 @@
         <v>46196</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35378,7 +35380,7 @@
         <v>46100</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35451,7 +35453,7 @@
         <v>46196</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35529,7 +35531,7 @@
         <v>46106</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35602,7 +35604,7 @@
         <v>46077</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35680,7 +35682,7 @@
         <v>46083</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35758,7 +35760,7 @@
         <v>46090</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35836,7 +35838,7 @@
         <v>46073</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35914,7 +35916,7 @@
         <v>46076</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35992,7 +35994,7 @@
         <v>46049</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36065,7 +36067,7 @@
         <v>46198</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36143,7 +36145,7 @@
         <v>46094</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36221,7 +36223,7 @@
         <v>46114</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36294,7 +36296,7 @@
         <v>46113</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36367,7 +36369,7 @@
         <v>45775</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36440,7 +36442,7 @@
         <v>46199</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36518,7 +36520,7 @@
         <v>46125</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36596,7 +36598,7 @@
         <v>45299</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36669,7 +36671,7 @@
         <v>46128</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36742,7 +36744,7 @@
         <v>44872</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36815,7 +36817,7 @@
         <v>45666</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36888,7 +36890,7 @@
         <v>46131</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36961,7 +36963,7 @@
         <v>46132</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37034,7 +37036,7 @@
         <v>46203</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37112,7 +37114,7 @@
         <v>46065</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37185,7 +37187,7 @@
         <v>45565</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37258,7 +37260,7 @@
         <v>45565</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37331,7 +37333,7 @@
         <v>46131</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37404,7 +37406,7 @@
         <v>46135</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37482,7 +37484,7 @@
         <v>46204</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37555,7 +37557,7 @@
         <v>45519</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37633,7 +37635,7 @@
         <v>45160</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37706,7 +37708,7 @@
         <v>46069</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37779,7 +37781,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37857,7 +37859,7 @@
         <v>45203</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37935,7 +37937,7 @@
         <v>46206</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38013,7 +38015,7 @@
         <v>46062</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38086,7 +38088,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38164,7 +38166,7 @@
         <v>46206</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38242,7 +38244,7 @@
         <v>46206</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38320,7 +38322,7 @@
         <v>46035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38393,7 +38395,7 @@
         <v>45264</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38466,7 +38468,7 @@
         <v>46162</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38544,7 +38546,7 @@
         <v>44790</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38622,7 +38624,7 @@
         <v>46205</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38700,7 +38702,7 @@
         <v>46211</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38778,7 +38780,7 @@
         <v>46211</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38856,7 +38858,7 @@
         <v>46213</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38934,7 +38936,7 @@
         <v>46213</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39012,7 +39014,7 @@
         <v>45862</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39085,7 +39087,7 @@
         <v>46213</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39163,7 +39165,7 @@
         <v>46224</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39241,7 +39243,7 @@
         <v>46224</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39319,7 +39321,7 @@
         <v>45062</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39397,7 +39399,7 @@
         <v>46226</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39475,7 +39477,7 @@
         <v>46272</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39548,7 +39550,7 @@
         <v>45111</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39626,7 +39628,7 @@
         <v>46272</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39699,7 +39701,7 @@
         <v>46273</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39777,7 +39779,7 @@
         <v>46227</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39855,7 +39857,7 @@
         <v>45544</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39928,7 +39930,7 @@
         <v>45615</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40001,7 +40003,7 @@
         <v>45507</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40074,7 +40076,7 @@
         <v>46232</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40147,7 +40149,7 @@
         <v>46111</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40225,7 +40227,7 @@
         <v>46275</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40298,7 +40300,7 @@
         <v>46275</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40371,7 +40373,7 @@
         <v>46232</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40449,7 +40451,7 @@
         <v>46232</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40527,7 +40529,7 @@
         <v>45099</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40600,7 +40602,7 @@
         <v>46276</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40673,7 +40675,7 @@
         <v>46276</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40746,7 +40748,7 @@
         <v>46276</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40819,7 +40821,7 @@
         <v>45222</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40892,7 +40894,7 @@
         <v>44753</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40965,7 +40967,7 @@
         <v>45076</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41038,7 +41040,7 @@
         <v>46281</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41111,7 +41113,7 @@
         <v>46237</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41189,7 +41191,7 @@
         <v>45544</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41262,7 +41264,7 @@
         <v>45525</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41335,7 +41337,7 @@
         <v>45617</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41408,7 +41410,7 @@
         <v>46282</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41486,7 +41488,7 @@
         <v>46282</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41564,7 +41566,7 @@
         <v>45238</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41637,7 +41639,7 @@
         <v>46282</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41715,7 +41717,7 @@
         <v>44622</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41788,7 +41790,7 @@
         <v>46282</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41866,7 +41868,7 @@
         <v>46282</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41944,7 +41946,7 @@
         <v>46282</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42022,7 +42024,7 @@
         <v>46282</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42100,7 +42102,7 @@
         <v>46282</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42178,7 +42180,7 @@
         <v>46281</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42256,7 +42258,7 @@
         <v>44887</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42329,7 +42331,7 @@
         <v>45212</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42402,7 +42404,7 @@
         <v>44732</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42475,7 +42477,7 @@
         <v>44910</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42553,7 +42555,7 @@
         <v>45610</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42631,7 +42633,7 @@
         <v>46289</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42704,7 +42706,7 @@
         <v>45699</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42777,7 +42779,7 @@
         <v>45699</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42850,7 +42852,7 @@
         <v>45610</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42923,7 +42925,7 @@
         <v>45554</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42996,7 +42998,7 @@
         <v>45757</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43069,7 +43071,7 @@
         <v>45544</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43142,7 +43144,7 @@
         <v>44711</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43220,7 +43222,7 @@
         <v>45593</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43293,7 +43295,7 @@
         <v>46248</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43366,7 +43368,7 @@
         <v>45561</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43439,7 +43441,7 @@
         <v>45615</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43512,7 +43514,7 @@
         <v>46294</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43590,7 +43592,7 @@
         <v>46294</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43668,7 +43670,7 @@
         <v>46295</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43741,7 +43743,7 @@
         <v>46295</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43814,7 +43816,7 @@
         <v>45096</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43892,7 +43894,7 @@
         <v>46294</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43970,7 +43972,7 @@
         <v>44711</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44048,7 +44050,7 @@
         <v>45628</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44121,7 +44123,7 @@
         <v>45628</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44194,7 +44196,7 @@
         <v>45628</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44267,7 +44269,7 @@
         <v>44620</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44340,7 +44342,7 @@
         <v>45301</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44413,7 +44415,7 @@
         <v>46244</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44491,7 +44493,7 @@
         <v>46244</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44564,7 +44566,7 @@
         <v>46147</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44637,7 +44639,7 @@
         <v>45988</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44710,7 +44712,7 @@
         <v>46297</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44783,7 +44785,7 @@
         <v>46254</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44856,7 +44858,7 @@
         <v>46290</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44929,7 +44931,7 @@
         <v>46232</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45002,7 +45004,7 @@
         <v>45782</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45075,7 +45077,7 @@
         <v>46300</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45148,7 +45150,7 @@
         <v>44985</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45221,7 +45223,7 @@
         <v>45301</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45294,7 +45296,7 @@
         <v>45561</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45367,7 +45369,7 @@
         <v>45687</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45440,7 +45442,7 @@
         <v>46301</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45518,7 +45520,7 @@
         <v>45440</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45596,7 +45598,7 @@
         <v>46302</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45669,7 +45671,7 @@
         <v>46302</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45742,7 +45744,7 @@
         <v>45575</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45820,7 +45822,7 @@
         <v>46259</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45898,7 +45900,7 @@
         <v>45790</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45971,7 +45973,7 @@
         <v>45790</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46049,7 +46051,7 @@
         <v>46259</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46122,7 +46124,7 @@
         <v>45251</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46195,7 +46197,7 @@
         <v>46303</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46268,7 +46270,7 @@
         <v>46303</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46341,7 +46343,7 @@
         <v>46303</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46414,7 +46416,7 @@
         <v>45266</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46487,7 +46489,7 @@
         <v>45790</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46560,7 +46562,7 @@
         <v>45331</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46633,7 +46635,7 @@
         <v>45307</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46706,7 +46708,7 @@
         <v>45615</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46779,7 +46781,7 @@
         <v>46261</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46857,7 +46859,7 @@
         <v>46261</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46935,7 +46937,7 @@
         <v>45800</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47013,7 +47015,7 @@
         <v>46308</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47091,7 +47093,7 @@
         <v>45043</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47164,7 +47166,7 @@
         <v>46265</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47237,7 +47239,7 @@
         <v>45810</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47310,7 +47312,7 @@
         <v>46308</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47383,7 +47385,7 @@
         <v>46308</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47461,7 +47463,7 @@
         <v>45056</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47534,7 +47536,7 @@
         <v>46268</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47607,7 +47609,7 @@
         <v>46268</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47680,7 +47682,7 @@
         <v>45699</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47753,7 +47755,7 @@
         <v>45812</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47831,7 +47833,7 @@
         <v>46311</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47909,7 +47911,7 @@
         <v>46311</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47987,7 +47989,7 @@
         <v>45817</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48065,7 +48067,7 @@
         <v>45817</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48143,7 +48145,7 @@
         <v>46295</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48216,7 +48218,7 @@
         <v>45826</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48289,7 +48291,7 @@
         <v>45834</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48362,7 +48364,7 @@
         <v>45836</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48435,7 +48437,7 @@
         <v>45839</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48508,7 +48510,7 @@
         <v>45839</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48581,7 +48583,7 @@
         <v>45841</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48654,7 +48656,7 @@
         <v>45848</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48727,7 +48729,7 @@
         <v>45848</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48800,7 +48802,7 @@
         <v>45848</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48873,7 +48875,7 @@
         <v>45848</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48946,7 +48948,7 @@
         <v>45848</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49019,7 +49021,7 @@
         <v>45848</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49092,7 +49094,7 @@
         <v>45859</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49170,7 +49172,7 @@
         <v>45217</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49243,7 +49245,7 @@
         <v>45870</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49321,7 +49323,7 @@
         <v>45875</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49399,7 +49401,7 @@
         <v>45877</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49477,7 +49479,7 @@
         <v>45881</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49550,7 +49552,7 @@
         <v>45376</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49628,7 +49630,7 @@
         <v>44960</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49701,7 +49703,7 @@
         <v>44960</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49774,7 +49776,7 @@
         <v>44907</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49852,7 +49854,7 @@
         <v>44498</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49930,7 +49932,7 @@
         <v>44637</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50008,7 +50010,7 @@
         <v>45377</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50086,7 +50088,7 @@
         <v>45567</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50159,7 +50161,7 @@
         <v>44589</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50237,7 +50239,7 @@
         <v>45377</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50315,7 +50317,7 @@
         <v>44498</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50393,7 +50395,7 @@
         <v>45159</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50466,7 +50468,7 @@
         <v>45315</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50544,7 +50546,7 @@
         <v>45699</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50622,7 +50624,7 @@
         <v>45938</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50700,7 +50702,7 @@
         <v>45938</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50778,7 +50780,7 @@
         <v>45938</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50856,7 +50858,7 @@
         <v>45938</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50934,7 +50936,7 @@
         <v>45957</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51007,7 +51009,7 @@
         <v>45938</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51085,7 +51087,7 @@
         <v>46133</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51158,7 +51160,7 @@
         <v>46258</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51236,7 +51238,7 @@
         <v>46261</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45492</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45705</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>45609</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46041</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45705</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45646</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45832</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>44867</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45672</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45832</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>46259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>46149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45939</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>46148</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>46239</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45890</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>46268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44714</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45159</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45351</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>46157</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>46204</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46008</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>46150</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45785</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>46030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45709</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45040</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45592</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>46008</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>46251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45531</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45783</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45947</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45901</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>46022</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>46000</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>46303</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>46303</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>46303</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>45877</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45376</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>46089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45904</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45966</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44509</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>46128</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>46211</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45987</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45376</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44827</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44498</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44620</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45299</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>46085</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45492</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>46148</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45960</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45966</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>46027</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>46206</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>46211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45160</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>46211</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>46224</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45628</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>46293</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>46309</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>46296</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45842</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44623</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44622</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44742</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44629</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44727</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44715</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44720</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44655</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44526</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>44735</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44497</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44497</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>45212</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>44729</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44545</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44888</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45229</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45484</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45595</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45314</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45306</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45757</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45209</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45736</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45582</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45353</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>44903</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44987</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>44896</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45758</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45222</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45441</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45264</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45274</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45407</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45132</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45223</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45610</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45477</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45601</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45062</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>44987</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45744</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44854</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45149</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45678</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45226</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>44844</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45267</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45223</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>44951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44985</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44788</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45301</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45030</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>44644</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45233</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45660</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>45135</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45481</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45782</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45775</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45159</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45422</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>45593</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>46139</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45222</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45887</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>44545</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45645</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45840</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>44914</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>46139</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45705</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>44693</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45647</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45138</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45894</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45705</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45894</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45152</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45896</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45698</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45862</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45768</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44644</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>46092</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>46049</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45091</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46044</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45797</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44644</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45848</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45353</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45903</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>46041</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45903</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45902</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>45904</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45758</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>45979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45881</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45793</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45744</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45915</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45915</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45915</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>46146</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45697</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>46146</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45923</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45736</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>46148</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45278</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>46150</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45932</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45209</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>44831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45103</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45986</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45628</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>46155</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45411</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45947</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45950</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45544</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>44964</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45954</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>46154</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45956</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>46106</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>46157</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45960</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45964</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>45316</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45628</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45223</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45966</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>45966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45968</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46161</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45971</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>46160</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45971</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>46163</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45975</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45974</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45975</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45974</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>46163</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45975</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45980</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45217</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44875</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45699</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45986</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45987</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45986</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45987</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45986</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46167</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45987</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46164</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45986</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>46164</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>46164</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45988</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45988</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45544</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45040</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45610</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45994</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45593</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45239</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45999</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45374</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45586</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45239</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45072</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45146</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45203</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45593</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>45206</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45674</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45113</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45113</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45999</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45593</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45252</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>45950</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45695</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>46174</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46171</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45180</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>46174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44627</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>46174</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45537</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>46009</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30097,7 +30097,7 @@
         <v>46008</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>46008</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>46008</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46008</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>46009</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>46010</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>46013</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45610</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>46024</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>46024</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>45303</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>46036</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46111</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>46177</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45453</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>46042</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46178</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>46111</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>46044</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>45826</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>46044</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>46111</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45113</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45111</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45014</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45688</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>46048</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45678</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46050</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>46050</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>46104</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46182</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>46052</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46057</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>46056</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46057</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>44917</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>46063</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>46189</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46070</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>44641</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>46188</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>44813</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46078</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>46076</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>46077</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>46077</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>46077</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>46076</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>46073</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>46077</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>46076</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46076</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>46190</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46190</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46090</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45638</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45638</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46190</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>46092</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46073</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>46189</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>46091</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>46073</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>46093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>45685</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45685</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>46098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>45238</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>46196</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>46100</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>46196</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>46106</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>46077</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>46083</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>46090</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>46073</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46076</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>46049</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>46198</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>46094</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>46114</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>46113</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45775</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>46199</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>46125</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45299</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>46128</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>44872</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45666</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>46131</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>46132</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>46203</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>46065</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45565</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45565</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>46131</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>46135</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>46204</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45519</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45160</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>46069</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>45203</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46206</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>46062</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46206</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>46206</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>46035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45264</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46162</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>44790</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>46205</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46211</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46211</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>46213</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>46213</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>45862</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>46213</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>46224</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>46224</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>45062</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>46226</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>46272</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45111</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46272</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>46273</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>46227</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>45544</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>45615</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>45507</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>46232</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>46111</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>46275</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>46275</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>46232</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>46232</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>45099</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>46276</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>46276</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>46276</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>45222</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44753</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45076</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46281</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46237</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45544</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>45525</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45617</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>46282</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>46282</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45238</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>46282</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>44622</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>46282</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>46282</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41946,7 +41946,7 @@
         <v>46282</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>46282</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>46282</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>46281</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44887</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45212</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44732</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>44910</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>45610</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>46289</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>45699</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45699</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45610</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45554</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>45757</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45544</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44711</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>45593</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>46248</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45561</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45615</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>46294</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46294</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>46295</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>46295</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>45096</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>46294</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>44711</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>45628</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>45628</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45628</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>44620</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45301</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>46244</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>46244</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>46147</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45988</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>46297</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>46254</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>46290</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>46232</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>45782</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45077,7 +45077,7 @@
         <v>46300</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>44985</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45301</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45296,7 +45296,7 @@
         <v>45561</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>45687</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>46301</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>45440</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>46302</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45671,7 +45671,7 @@
         <v>46302</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45575</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>46259</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45790</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         <v>45790</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>46259</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45251</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>46303</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>46303</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>46303</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46416,7 +46416,7 @@
         <v>45266</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46489,7 +46489,7 @@
         <v>45790</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45331</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>45307</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>45615</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>46261</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>46261</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45800</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46308</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45043</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>46265</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45810</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>46308</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>46308</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45056</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>46268</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>46268</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>45699</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45812</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>46311</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46311</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>45817</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45817</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>46295</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45826</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45834</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45836</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         <v>45839</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>45839</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45841</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45848</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>45848</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>45848</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45848</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>45848</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>45848</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45859</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49172,7 +49172,7 @@
         <v>45217</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>45870</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45875</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45877</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45881</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>45376</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>44960</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>44960</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>44907</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>44498</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>44637</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45377</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45567</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>44589</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45377</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>44498</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>45159</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45315</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45699</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50624,7 +50624,7 @@
         <v>45938</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45938</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50780,7 +50780,7 @@
         <v>45938</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45938</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>45957</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45938</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>46133</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>46258</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46261</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>45223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45492</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45609</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45705</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46041</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45705</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45646</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44867</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45832</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45882</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45672</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>46259</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45832</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>45219</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>45939</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>46148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45890</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>46268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44714</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45159</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>46008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45351</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>46204</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>46150</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>46008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>46262</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>46157</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>46030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45592</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>46251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>45947</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>46008</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>45709</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45040</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45901</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>46000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>46303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>46303</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45832</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>45877</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>46303</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>46022</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45376</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>46089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45966</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46211</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45782</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45987</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>46128</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44509</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45833</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45376</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44827</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44498</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44620</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45628</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45960</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45966</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45966</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>46199</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>46211</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>46211</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>46224</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>46027</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>46293</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45842</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>46309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>46296</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>46085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>46148</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>45160</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45299</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45492</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44623</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44622</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44742</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44629</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44727</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44715</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44720</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44655</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44526</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>44735</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44497</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44497</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>45887</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>44813</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45678</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45698</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45894</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44987</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45894</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44888</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45896</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45316</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45902</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45903</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44732</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45904</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45209</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45793</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>44952</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>46161</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45915</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46163</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45915</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45915</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45915</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>46164</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>46164</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45628</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>46164</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>46163</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>46167</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45678</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44711</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45923</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45217</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45096</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>46167</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44875</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>46171</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45507</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>46174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45407</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>46174</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45422</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>46177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45132</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45223</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>46111</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44903</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45615</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45950</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45947</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46111</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45303</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>46111</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>46104</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>46182</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45956</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45954</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45301</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45411</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45593</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>46189</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45610</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>46189</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>46189</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45964</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45966</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>46188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45966</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>46190</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45062</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>46190</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45223</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45968</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45971</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45971</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>46196</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45974</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>46196</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>45974</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>46198</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45975</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45975</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45209</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45975</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46199</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45699</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45980</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>46203</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45736</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45222</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>46162</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>46205</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45986</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>46204</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45986</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45986</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>46206</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45617</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>46206</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45987</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45988</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46206</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>46206</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>45987</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45987</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45988</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>46206</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>46211</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45699</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45699</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45775</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>46211</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45484</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>46213</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>46213</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>45994</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>46213</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45695</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45862</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45601</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45264</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45113</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45113</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45586</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45950</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>45252</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45999</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45239</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45113</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45674</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45374</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45593</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45593</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45072</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45203</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45206</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>45999</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45999</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45834</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45239</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45593</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45104</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>46224</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45782</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>46224</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>46226</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>46227</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45301</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45440</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>45561</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>46008</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44985</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>46008</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>46111</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>46232</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>46232</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>46232</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>46008</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>46008</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45687</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>46237</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45575</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>46009</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>46010</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>46013</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46281</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45790</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45790</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>46282</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46282</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>46024</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>45790</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>46024</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>46282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>46282</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>46282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46282</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>46282</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45266</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45251</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>46036</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>44887</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45331</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46281</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45537</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>46042</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45307</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45615</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>46044</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>46044</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45826</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46048</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45800</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46050</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46050</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>46052</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>46289</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>45043</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>46056</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>46057</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>46057</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45056</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45810</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46248</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45699</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45812</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46294</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>46294</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>46294</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>46070</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46076</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>46076</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>46077</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46295</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46295</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>46077</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>46076</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>46077</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>46076</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46077</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46073</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45826</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>46078</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46297</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>46244</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46244</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45834</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45836</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46091</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46090</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>46092</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46073</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>46147</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45839</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46073</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46093</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45544</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45839</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46300</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45481</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45841</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>46098</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>46290</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>46100</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>46232</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45441</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>46254</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45848</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46077</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46302</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45848</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45848</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45848</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45848</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46083</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>46259</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>46049</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>46106</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46259</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>46302</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>46076</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>46073</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>46090</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>46094</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45859</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>46113</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>46301</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45217</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>46114</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>46261</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45870</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46125</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>46303</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>46261</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>46303</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45875</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>46131</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46128</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46132</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45877</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46131</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>46065</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>46265</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46308</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45881</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>45138</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46308</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45647</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46308</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>46069</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>46135</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45519</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45301</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45660</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>46295</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45645</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45768</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45758</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45775</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>46139</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>46311</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>46311</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>46268</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45782</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45160</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46139</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45840</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45881</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46268</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>46092</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45797</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>46062</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>46272</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45593</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46044</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>46316</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45848</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45862</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>46316</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>46316</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>46035</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>46273</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44917</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45244</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>46272</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>46041</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>46275</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>46066</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>46317</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46318</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45979</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>44951</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46049</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46276</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>46276</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45903</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>46276</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>46275</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>46146</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>46146</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>46317</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>45544</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>46148</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45233</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>46150</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>44622</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45986</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>46106</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45544</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>46154</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>46155</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>46157</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45610</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>46160</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>45565</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45099</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45314</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>45628</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45565</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>44831</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>45610</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45697</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>45554</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>44985</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45113</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45477</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45544</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>44844</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45685</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45685</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45705</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45091</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45212</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>45212</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>44910</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45238</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45736</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45111</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45757</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44914</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>44872</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45135</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44753</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44644</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45757</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45103</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45353</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45099</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45222</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44964</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>44788</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45014</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>44896</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45353</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45561</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45152</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>44790</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45030</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45544</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45149</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>45267</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45610</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45638</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>45638</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44620</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45758</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45223</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>44545</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>44644</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45582</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45610</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47191,7 +47191,7 @@
         <v>44644</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>44641</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>45159</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45453</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>45628</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>45615</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>44729</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45666</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45111</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45180</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45688</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45705</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45113</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45274</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>44711</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>45222</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45203</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45299</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45229</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45238</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45744</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45306</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>44693</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>44854</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45264</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45076</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45040</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45744</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45278</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45226</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>44627</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>44987</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45595</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45628</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45628</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45316</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>44545</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>45525</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>44637</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>44589</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>45376</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>44960</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>44960</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>44907</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44498</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45377</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>45567</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45377</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50780,7 +50780,7 @@
         <v>44498</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45159</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45315</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45699</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45938</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45938</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45938</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45938</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51399,7 +51399,7 @@
         <v>45938</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45957</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>46133</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46261</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>46258</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>

--- a/Översikt ORSA.xlsx
+++ b/Översikt ORSA.xlsx
@@ -601,7 +601,7 @@
         <v>45271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>45195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>44935</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45867</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>45223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>45204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45492</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45609</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45705</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46041</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45705</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45646</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44867</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45832</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45882</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45672</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>46259</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45832</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>45219</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>45939</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>46148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45890</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>46268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44714</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45159</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>46008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45351</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>46204</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>46150</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>46008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>46262</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>46157</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>46030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45592</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>46251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>45947</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>46008</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>45709</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45040</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45901</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>46000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>46303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>46303</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45832</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>45877</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>46303</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>46022</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45376</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>46089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45966</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46211</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45782</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45987</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>46128</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44509</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45833</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45376</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44827</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44498</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46089</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44620</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45628</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45960</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45966</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45966</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>46199</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>46211</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>46211</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>46224</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>46027</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>46293</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45842</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>46309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>46296</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>46085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>46148</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>45160</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45299</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45492</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44623</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44622</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44742</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44629</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44727</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44715</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44720</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44655</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44526</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>44735</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44497</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44497</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>45887</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>44813</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45678</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45698</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45894</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44987</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45894</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44888</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45896</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45316</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45902</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45903</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44732</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45904</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45209</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45793</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>44952</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>46161</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45915</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46163</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45915</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45915</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45915</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>46164</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>46164</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45628</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>46164</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>46163</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>46167</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45678</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44711</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45923</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45217</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45096</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>46167</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44875</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>46171</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45507</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>46174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45407</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>46174</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45422</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>46177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45132</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45223</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>46111</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44903</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45615</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45950</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45947</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46111</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45303</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>46111</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>46104</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>46182</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45956</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45954</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45301</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45411</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45593</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>46189</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45610</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>46189</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>46189</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45964</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45966</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>46188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45966</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>46190</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45062</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>46190</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45223</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45968</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45971</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45971</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>46196</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45974</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>46196</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>45974</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>46198</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45975</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45975</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45209</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45975</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46199</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45699</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45980</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>46203</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45736</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45222</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>46162</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>46205</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45986</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>46204</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45986</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45986</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>46206</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45617</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>46206</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45987</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45988</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46206</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>46206</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>45987</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45987</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45988</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>46206</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>46211</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45699</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45699</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45775</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>46211</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45484</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>46213</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>46213</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>45994</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>46213</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45695</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45862</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45601</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45264</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45113</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45113</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45586</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45950</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>45252</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45999</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45239</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45113</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45674</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45374</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45593</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45593</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45072</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45203</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45206</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>45999</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45999</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45834</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45239</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45593</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45104</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>46224</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45782</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>46224</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>46226</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>46227</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45301</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45440</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>45561</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>46008</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44985</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>46008</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>46111</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>46232</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>46232</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>46232</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>46008</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>46008</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45687</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>46237</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45575</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>46009</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>46010</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>46013</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46281</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45790</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45790</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>46282</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46282</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>46024</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>45790</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>46024</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>46282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>46282</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>46282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46282</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>46282</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45266</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45251</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>46036</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>44887</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45331</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46281</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45537</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>46042</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45307</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45615</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>46044</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>46044</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45826</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46048</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45800</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46050</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46050</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>46052</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>46289</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>45043</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>46056</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>46057</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>46057</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45056</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45810</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46248</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45699</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45812</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46294</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>46294</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>46294</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>46070</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46076</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>46076</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>46077</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46295</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46295</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>46077</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>46076</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>46077</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>46076</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46077</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46073</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45826</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>46078</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46297</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>46244</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46244</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45834</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45836</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46091</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46090</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>46092</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46073</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>46147</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45839</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46073</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46093</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45544</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45839</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46300</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45481</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45841</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>46098</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>46290</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>46100</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>46232</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45441</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>46254</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45848</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46077</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46302</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45848</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45848</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45848</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45848</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46083</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>46259</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>46049</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>46106</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46259</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>46302</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>46076</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>46073</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>46090</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>46094</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45859</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>46113</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>46301</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45217</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>46114</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>46261</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45870</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46125</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>46303</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>46261</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>46303</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45875</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>46131</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46128</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46132</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45877</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46131</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>46065</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>46265</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46308</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45881</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>45138</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46308</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45647</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46308</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>46069</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>46135</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45519</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45301</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45660</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>46295</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45645</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45768</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45758</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45775</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>46139</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>46311</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>46311</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>46268</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45782</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45160</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46139</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45840</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45881</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46268</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>46092</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45797</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>46062</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>46272</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45593</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46044</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>46316</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45848</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45862</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>46316</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>46316</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>46035</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>46273</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44917</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45244</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>46272</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>46041</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>46275</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>46066</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>46317</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46318</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45979</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>44951</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46049</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46276</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>46276</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45903</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>46276</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>46275</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>46146</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>46146</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>46317</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>45544</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>46148</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45233</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>46150</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>44622</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45986</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>46106</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45544</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>46154</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>46155</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>46157</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45610</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>46160</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>45565</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45099</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45314</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>45628</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45565</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>44831</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>45610</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45697</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>45554</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>44985</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45113</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45477</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45544</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>44844</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45685</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45685</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45705</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45091</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45212</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>45212</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>44910</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45238</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45736</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45111</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45757</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44914</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>44872</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45135</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44753</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44644</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45757</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45103</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45353</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45099</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45222</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44964</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>44788</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45014</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>44896</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45353</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45561</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45152</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>44790</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45030</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45544</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45149</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>45267</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45610</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45638</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>45638</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44620</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45758</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45223</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>44545</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>44644</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45582</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45610</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47191,7 +47191,7 @@
         <v>44644</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>44641</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>45159</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45453</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>45628</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>45615</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>44729</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45666</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45111</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45180</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45688</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45705</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45113</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45274</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>44711</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>45222</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45203</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45299</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45229</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45238</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45744</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45306</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>44693</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>44854</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45264</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45076</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45040</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45744</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45278</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45226</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>44627</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>44987</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45595</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45628</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45628</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45316</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>44545</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>45525</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>44637</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>44589</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>45376</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>44960</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>44960</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>44907</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44498</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45377</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>45567</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45377</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50780,7 +50780,7 @@
         <v>44498</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45159</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45315</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45699</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45938</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45938</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45938</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45938</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51399,7 +51399,7 @@
         <v>45938</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45957</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>46133</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46261</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>46258</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
